--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA107ECC-3506-5C40-A3CF-8DE49BBF05B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3CA8E4-2A28-254B-AF6A-97D4891DAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
   <si>
     <t>blank</t>
   </si>
@@ -125,9 +125,6 @@
     <t>slide-content</t>
   </si>
   <si>
-    <t>Ibn Ḥazm</t>
-  </si>
-  <si>
     <t>Ibn Taymiyya</t>
   </si>
   <si>
@@ -258,6 +255,12 @@
   </si>
   <si>
     <t>damascus-citadel.jpg</t>
+  </si>
+  <si>
+    <t>Muslimisch-jüdischer Austausch</t>
+  </si>
+  <si>
+    <t>Christlich-muslimischer Austausch</t>
   </si>
 </sst>
 </file>
@@ -325,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -355,6 +358,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,7 +775,7 @@
         <v>18</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" t="str">
@@ -783,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L2" t="str">
         <f>B2&amp;"-"&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(F2,"[\.\s\-:–]","-"),"\-+","-")</f>
@@ -791,11 +795,11 @@
       </c>
       <c r="N2" s="9"/>
       <c r="P2" t="str">
-        <f t="shared" ref="P2:P16" si="2">"["&amp;B2&amp;"]"</f>
+        <f t="shared" ref="P2" si="2">"["&amp;B2&amp;"]"</f>
         <v>[1]</v>
       </c>
       <c r="Q2" t="str">
-        <f t="shared" ref="Q2:Q15" si="3">"---
+        <f t="shared" ref="Q2" si="3">"---
 layout: post
 " &amp; B$1 &amp; ": " &amp; B2 &amp; "
 " &amp; P$1 &amp; ": " &amp; P2 &amp; "
@@ -918,10 +922,10 @@
         <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" t="str">
@@ -933,7 +937,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L16" si="5">B3&amp;"-"&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(F3,"[\.\s\-:–]","-"),"\-+","-")</f>
@@ -1062,28 +1066,28 @@
         <f t="shared" si="0"/>
         <v>2025-10-30-3.md</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>30</v>
+      <c r="E4" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="4"/>
-        <v>3. Ibn Ḥazm: Bibelkritik</v>
+        <v>3. Muslimisch-jüdischer Austausch: Bibelkritik</v>
       </c>
       <c r="J4" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L4" t="str">
         <f t="shared" si="5"/>
@@ -1182,28 +1186,28 @@
         <f t="shared" si="0"/>
         <v>2025-11-06-4.md</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>30</v>
+      <c r="E5" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="4"/>
-        <v>4. Ibn Ḥazm: Ibn Ḥazm: Text</v>
+        <v>4. Muslimisch-jüdischer Austausch: Ibn Ḥazm: Text</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L5" t="str">
         <f t="shared" si="5"/>
@@ -1302,28 +1306,28 @@
         <f t="shared" si="0"/>
         <v>2025-11-13-5.md</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>30</v>
+      <c r="E6" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="4"/>
-        <v>5. Ibn Ḥazm: Argumentationsanalyse</v>
+        <v>5. Muslimisch-jüdischer Austausch: Argumentationsanalyse</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L6" t="str">
         <f t="shared" si="5"/>
@@ -1422,26 +1426,26 @@
         <f t="shared" si="0"/>
         <v>2025-11-20-6.md</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>30</v>
+      <c r="E7" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" t="str">
         <f t="shared" si="4"/>
-        <v>6. Ibn Ḥazm: Ibn Ḥazm: Argumentationsanalyse</v>
+        <v>6. Muslimisch-jüdischer Austausch: Ibn Ḥazm: Argumentationsanalyse</v>
       </c>
       <c r="J7" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L7" t="str">
         <f t="shared" si="5"/>
@@ -1540,28 +1544,28 @@
         <f t="shared" si="0"/>
         <v>2025-11-27-7.md</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>30</v>
+      <c r="E8" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="4"/>
-        <v>7. Ibn Ḥazm: Salomo ibn Adret: Text</v>
+        <v>7. Muslimisch-jüdischer Austausch: Salomo ibn Adret: Text</v>
       </c>
       <c r="J8" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L8" t="str">
         <f t="shared" si="5"/>
@@ -1660,28 +1664,28 @@
         <f t="shared" si="0"/>
         <v>2025-12-04-8.md</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>30</v>
+      <c r="E9" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="4"/>
-        <v>8. Ibn Ḥazm: Salomo ibn Adret: Argumentationsanalyse</v>
+        <v>8. Muslimisch-jüdischer Austausch: Salomo ibn Adret: Argumentationsanalyse</v>
       </c>
       <c r="J9" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" t="str">
         <f t="shared" si="5"/>
@@ -1781,25 +1785,25 @@
         <v>2025-12-11-9.md</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" t="str">
         <f t="shared" si="4"/>
-        <v>9. Ibn Taymiyya: Brief aus Zypern</v>
+        <v>9. Christlich-muslimischer Austausch: Brief aus Zypern</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L10" t="str">
         <f t="shared" si="5"/>
@@ -1899,25 +1903,25 @@
         <v>2025-12-18-10.md</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" t="str">
         <f t="shared" si="4"/>
-        <v>10. Ibn Taymiyya: Brief aus Zypern: Text</v>
+        <v>10. Christlich-muslimischer Austausch: Brief aus Zypern: Text</v>
       </c>
       <c r="J11" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L11" t="str">
         <f t="shared" si="5"/>
@@ -2017,27 +2021,27 @@
         <v>2026-01-15-11.md</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="4"/>
-        <v>11. Ibn Taymiyya: Brief aus Zypern: Argumentationsanalyse</v>
+        <v>11. Christlich-muslimischer Austausch: Brief aus Zypern: Argumentationsanalyse</v>
       </c>
       <c r="J12" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="K12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L12" t="str">
         <f t="shared" si="5"/>
@@ -2137,25 +2141,25 @@
         <v>2026-01-22-12.md</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H13" s="7"/>
       <c r="I13" t="str">
         <f t="shared" si="4"/>
-        <v>12. Ibn Taymiyya: Ibn Taymiyya</v>
+        <v>12. Christlich-muslimischer Austausch: Ibn Taymiyya</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="K13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L13" t="str">
         <f t="shared" si="5"/>
@@ -2255,25 +2259,25 @@
         <v>2026-01-29-13.md</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" t="str">
         <f t="shared" si="4"/>
-        <v>13. Ibn Taymiyya: Ibn Taymiyya: Text</v>
+        <v>13. Christlich-muslimischer Austausch: Ibn Taymiyya: Text</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L14" t="str">
         <f t="shared" si="5"/>
@@ -2373,13 +2377,13 @@
         <v>2026-02-05-14.md</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" t="str">
@@ -2391,7 +2395,7 @@
         <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L15" t="str">
         <f t="shared" si="5"/>
@@ -2491,13 +2495,13 @@
         <v>2026-02-12-15.md</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" t="str">
@@ -2509,7 +2513,7 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L16" t="str">
         <f t="shared" si="5"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3CA8E4-2A28-254B-AF6A-97D4891DAE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662F0964-174E-3A4C-A836-C6B9B1953296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
   <si>
     <t>blank</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>Christlich-muslimischer Austausch</t>
+  </si>
+  <si>
+    <t>whittinghamIntroduction2020</t>
   </si>
 </sst>
 </file>
@@ -1093,6 +1096,9 @@
         <f t="shared" si="5"/>
         <v>3-Bibelkritik</v>
       </c>
+      <c r="M4" t="s">
+        <v>76</v>
+      </c>
       <c r="N4" s="9"/>
       <c r="P4" t="str">
         <f t="shared" si="6"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662F0964-174E-3A4C-A836-C6B9B1953296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BDF8E1-3D42-C04A-B904-DF7B827C0778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
   <si>
     <t>blank</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>whittinghamIntroduction2020</t>
+  </si>
+  <si>
+    <t>adangMedievalMuslimPolemics1999</t>
   </si>
 </sst>
 </file>
@@ -946,6 +949,9 @@
         <f t="shared" ref="L3:L16" si="5">B3&amp;"-"&amp;_xlfn.REGEXREPLACE(_xlfn.REGEXREPLACE(F3,"[\.\s\-:–]","-"),"\-+","-")</f>
         <v>2-Polemiken</v>
       </c>
+      <c r="M3" t="s">
+        <v>77</v>
+      </c>
       <c r="N3" s="9"/>
       <c r="P3" t="str">
         <f t="shared" ref="P3:P16" si="6">"["&amp;B3&amp;"]"</f>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BDF8E1-3D42-C04A-B904-DF7B827C0778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E315773-3D7C-5344-BCE1-F9406336299B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>blank</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>adangMedievalMuslimPolemics1999</t>
+  </si>
+  <si>
+    <t>Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.</t>
   </si>
 </sst>
 </file>
@@ -952,7 +955,9 @@
       <c r="M3" t="s">
         <v>77</v>
       </c>
-      <c r="N3" s="9"/>
+      <c r="N3" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="P3" t="str">
         <f t="shared" ref="P3:P16" si="6">"["&amp;B3&amp;"]"</f>
         <v>[2]</v>
@@ -1012,7 +1017,7 @@
 ## Einleitung
 ## Heutiges Lernziel
 "&amp;N3</f>
-        <v xml:space="preserve"># Interreligiöse Begegnungen und Debatten auf Arabisch vom 11. bis zum 14. Jahrhundert
+        <v># Interreligiöse Begegnungen und Debatten auf Arabisch vom 11. bis zum 14. Jahrhundert
 {: .r-fit-text}
 ### Was sind Polemiken und wofür sollen sie analysiert werden?
 Sommersemester 2025
@@ -1022,7 +1027,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-</v>
+Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.</v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U16" si="11">"
@@ -1058,6 +1063,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
+Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1145,6 +1151,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
+Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1177,6 +1184,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
+Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E315773-3D7C-5344-BCE1-F9406336299B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0798DD0-561D-1945-ABE0-33C24348BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>blank</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>Die Disputationsliteratur als eine Textgattung mit ihrer Tendenzen und Interpretationshürden erklären.</t>
+  </si>
+  <si>
+    <t>eemerenAnalysisReconstruction2003</t>
+  </si>
+  <si>
+    <t>adangIbnHazmAuthors1996, ibnhazmKitabAlfisalFi</t>
+  </si>
+  <si>
+    <t>Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1242,12 @@
         <f t="shared" si="5"/>
         <v>4-Ibn-Ḥazm-Text</v>
       </c>
-      <c r="N5" s="9"/>
+      <c r="M5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="P5" t="str">
         <f t="shared" si="6"/>
         <v>[4]</v>
@@ -1267,7 +1281,7 @@
       </c>
       <c r="T5" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"># Interreligiöse Begegnungen und Debatten auf Arabisch vom 11. bis zum 14. Jahrhundert
+        <v># Interreligiöse Begegnungen und Debatten auf Arabisch vom 11. bis zum 14. Jahrhundert
 {: .r-fit-text}
 ### Was hat Ibn Hazm über die Bibel geschrieben?
 Sommersemester 2025
@@ -1277,7 +1291,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
-</v>
+Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.</v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="11"/>
@@ -1309,6 +1323,7 @@
 ## Projekt
 ## Einleitung
 ## Heutiges Lernziel
+Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.
 ## Lektüre
 ## Diskussion
 ## Vorschau
@@ -1352,6 +1367,9 @@
       <c r="L6" t="str">
         <f t="shared" si="5"/>
         <v>5-Argumentationsanalyse</v>
+      </c>
+      <c r="M6" t="s">
+        <v>79</v>
       </c>
       <c r="N6" s="9"/>
       <c r="P6" t="str">
@@ -1393,6 +1411,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
+Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung
@@ -1425,6 +1444,7 @@
 Sommersemester 2025
 Prof. Dr. Nathan Gibson
 ## 📈 Rückblick: Lernziel
+Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.
 ## 📈 Rückblick: 
 ## Projekt
 ## Einleitung

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0798DD0-561D-1945-ABE0-33C24348BB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1A5C46-2EEB-9D4C-AE72-4E4B2C0CFBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="46320" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
   <si>
     <t>blank</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>Die Kritik von Ibn Ḥazm an den Tanakh in seinem Kontext (Andalusien, 11. Jhdt.) grob skizzieren.</t>
+  </si>
+  <si>
+    <t>ibnhazmKitabAlfisalFia</t>
   </si>
 </sst>
 </file>
@@ -1491,6 +1494,9 @@
         <f t="shared" si="5"/>
         <v>6-Ibn-Ḥazm-Argumentationsanalyse</v>
       </c>
+      <c r="M7" t="s">
+        <v>82</v>
+      </c>
       <c r="N7" s="9"/>
       <c r="P7" t="str">
         <f t="shared" si="6"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE1A5C46-2EEB-9D4C-AE72-4E4B2C0CFBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECDBA8F-BCFF-3B47-8C1A-D1DF976FA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
   <si>
     <t>blank</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>ibnhazmKitabAlfisalFia</t>
+  </si>
+  <si>
+    <t>adangJewishReplyIbn2002</t>
   </si>
 </sst>
 </file>
@@ -1617,6 +1620,9 @@
         <f t="shared" si="5"/>
         <v>7-Salomo-ibn-Adret-Text</v>
       </c>
+      <c r="M8" t="s">
+        <v>83</v>
+      </c>
       <c r="N8" s="9"/>
       <c r="P8" t="str">
         <f t="shared" si="6"/>
@@ -1737,6 +1743,9 @@
         <f t="shared" si="5"/>
         <v>8-Salomo-ibn-Adret-Argumentationsanalyse</v>
       </c>
+      <c r="M9" t="s">
+        <v>83</v>
+      </c>
       <c r="N9" s="9"/>
       <c r="P9" t="str">
         <f t="shared" si="6"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECDBA8F-BCFF-3B47-8C1A-D1DF976FA234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572C1E5E-9C92-4540-81A0-94941F3CCCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
   <si>
     <t>blank</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>adangJewishReplyIbn2002</t>
+  </si>
+  <si>
+    <t>ibntaymiyyaIITahrifCorruption1985, suleiman2IbnTaymiyyas2019</t>
   </si>
 </sst>
 </file>
@@ -2220,6 +2223,9 @@
         <f t="shared" si="5"/>
         <v>12-Ibn-Taymiyya</v>
       </c>
+      <c r="M13" t="s">
+        <v>84</v>
+      </c>
       <c r="N13" s="9"/>
       <c r="P13" t="str">
         <f t="shared" si="6"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572C1E5E-9C92-4540-81A0-94941F3CCCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29362D-1082-F84B-A7C5-F23FBE410757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4880" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="87">
   <si>
     <t>blank</t>
   </si>
@@ -288,6 +288,12 @@
   </si>
   <si>
     <t>ibntaymiyyaIITahrifCorruption1985, suleiman2IbnTaymiyyas2019</t>
+  </si>
+  <si>
+    <t>ebiedLettersTheirAuthors2005</t>
+  </si>
+  <si>
+    <t>ebiedLetterPeopleCyprus2005a</t>
   </si>
 </sst>
 </file>
@@ -1867,6 +1873,9 @@
         <f t="shared" si="5"/>
         <v>9-Brief-aus-Zypern</v>
       </c>
+      <c r="M10" t="s">
+        <v>85</v>
+      </c>
       <c r="N10" s="9"/>
       <c r="P10" t="str">
         <f t="shared" si="6"/>
@@ -1985,6 +1994,9 @@
         <f t="shared" si="5"/>
         <v>10-Brief-aus-Zypern-Text</v>
       </c>
+      <c r="M11" t="s">
+        <v>86</v>
+      </c>
       <c r="N11" s="9"/>
       <c r="P11" t="str">
         <f t="shared" si="6"/>
@@ -2105,6 +2117,9 @@
         <f t="shared" si="5"/>
         <v>11-Brief-aus-Zypern-Argumentationsanalyse</v>
       </c>
+      <c r="M12" t="s">
+        <v>86</v>
+      </c>
       <c r="N12" s="9"/>
       <c r="P12" t="str">
         <f t="shared" si="6"/>

--- a/_data/sessions.xlsx
+++ b/_data/sessions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathan/Github/jirelations/25debatten/_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A29362D-1082-F84B-A7C5-F23FBE410757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB704C20-A961-A046-8F42-D7E7C45A4FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="500" windowWidth="33720" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
     <t>ebiedLettersTheirAuthors2005</t>
   </si>
   <si>
-    <t>ebiedLetterPeopleCyprus2005a</t>
+    <t>ebiedLetterPeopleCyprus2005</t>
   </si>
 </sst>
 </file>
